--- a/data/WHRS - INPUT FILE.xlsx
+++ b/data/WHRS - INPUT FILE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VENKAT\Downloads\LEARNING\WHRS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD382661-F850-4DD5-B40D-ABF703D93631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFB9AAA-4D86-481A-89A2-5CFA18ED4682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="40">
   <si>
     <t>DATE TIME</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>DRIFT</t>
+  </si>
+  <si>
+    <t>ANCHOR</t>
   </si>
 </sst>
 </file>
@@ -506,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98285ED0-D7B4-4999-8381-C6FAA6472CB0}">
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC43"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21.3984375" bestFit="1" customWidth="1"/>
@@ -3138,6 +3141,12 @@
       <c r="T32" t="s">
         <v>37</v>
       </c>
+      <c r="U32">
+        <v>45368</v>
+      </c>
+      <c r="V32">
+        <v>47571</v>
+      </c>
       <c r="W32">
         <v>0</v>
       </c>
@@ -3167,6 +3176,12 @@
       <c r="T33" t="s">
         <v>37</v>
       </c>
+      <c r="U33">
+        <v>45368</v>
+      </c>
+      <c r="V33">
+        <v>47571</v>
+      </c>
       <c r="W33">
         <v>0</v>
       </c>
@@ -3196,6 +3211,12 @@
       <c r="T34" t="s">
         <v>37</v>
       </c>
+      <c r="U34">
+        <v>45368</v>
+      </c>
+      <c r="V34">
+        <v>47571</v>
+      </c>
       <c r="W34">
         <v>0</v>
       </c>
@@ -3225,6 +3246,12 @@
       <c r="T35" t="s">
         <v>37</v>
       </c>
+      <c r="U35">
+        <v>45368</v>
+      </c>
+      <c r="V35">
+        <v>47571</v>
+      </c>
       <c r="W35">
         <v>0</v>
       </c>
@@ -3254,6 +3281,12 @@
       <c r="T36" t="s">
         <v>37</v>
       </c>
+      <c r="U36">
+        <v>45368</v>
+      </c>
+      <c r="V36">
+        <v>47571</v>
+      </c>
       <c r="W36">
         <v>0</v>
       </c>
@@ -3714,9 +3747,35 @@
         <v>37</v>
       </c>
     </row>
+    <row r="43" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A43" s="1">
+        <v>46293.166666608799</v>
+      </c>
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43">
+        <v>0</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+      <c r="F43">
+        <v>79</v>
+      </c>
+      <c r="G43">
+        <v>80</v>
+      </c>
+      <c r="T43" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A42" xr:uid="{529D23C2-FC55-463A-98AF-63DCB03A4894}">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A43" xr:uid="{529D23C2-FC55-463A-98AF-63DCB03A4894}">
       <formula1>AND(ISNUMBER(A2),A2=INT(A2)+MOD(A2,1))</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/WHRS - INPUT FILE.xlsx
+++ b/data/WHRS - INPUT FILE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VENKAT\Downloads\LEARNING\WHRS\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFFB9AAA-4D86-481A-89A2-5CFA18ED4682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CC206D-308E-455F-8B95-DDE0750CE1BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3746,6 +3746,15 @@
       <c r="T42" t="s">
         <v>37</v>
       </c>
+      <c r="U42">
+        <v>60888</v>
+      </c>
+      <c r="V42">
+        <v>63776</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
     </row>
     <row r="43" spans="1:28" x14ac:dyDescent="0.45">
       <c r="A43" s="1">
@@ -3771,6 +3780,15 @@
       </c>
       <c r="T43" t="s">
         <v>37</v>
+      </c>
+      <c r="U43">
+        <v>60888</v>
+      </c>
+      <c r="V43">
+        <v>63776</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
